--- a/9V_Converter/9V_Converter_bom.xlsx
+++ b/9V_Converter/9V_Converter_bom.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10719"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10313"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/andrei/Documents/GitHub/Midi-boards/9V_Converter/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E85C0BC2-4D6E-FE45-8DF6-DF1027DACDEC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8980B857-60FB-2C46-8E5C-2AF51F188DBE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="33600" windowHeight="19280" xr2:uid="{B1A2F949-7E6C-8644-8E19-B56F3D22CDD7}"/>
+    <workbookView xWindow="0" yWindow="780" windowWidth="33600" windowHeight="19280" xr2:uid="{B1A2F949-7E6C-8644-8E19-B56F3D22CDD7}"/>
   </bookViews>
   <sheets>
     <sheet name="midithru10" sheetId="1" r:id="rId1"/>
@@ -428,9 +428,6 @@
     <t>2.54mm jumper</t>
   </si>
   <si>
-    <t>80-pin 2.54mm header strip</t>
-  </si>
-  <si>
     <t>3-pin 2.54mm male header</t>
   </si>
   <si>
@@ -438,6 +435,9 @@
   </si>
   <si>
     <t>* JP1 bypasses 9V power regulator if desired</t>
+  </si>
+  <si>
+    <t>40-pin 2.54mm header strip</t>
   </si>
 </sst>
 </file>
@@ -1783,7 +1783,7 @@
         <v>118</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="D29" s="3" t="s">
         <v>116</v>
@@ -1813,7 +1813,7 @@
         <v>46</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="D30" s="3"/>
       <c r="E30" s="3">
@@ -1826,7 +1826,7 @@
         <v>117</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="D31" s="3"/>
       <c r="E31" s="3">
@@ -2033,7 +2033,7 @@
     </row>
     <row r="44" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A44" s="16" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B44" s="17"/>
       <c r="C44" s="17"/>
